--- a/data/raw/inventory/Week 30/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -3499,7 +3499,7 @@
         <v>16</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50" t="n">
         <v>17</v>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F75" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -5064,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F128" t="n">
         <v>196</v>
@@ -8347,10 +8347,10 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K128" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
@@ -10316,7 +10316,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F160" t="n">
         <v>72</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -10936,10 +10936,10 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F170" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
@@ -14656,7 +14656,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F230" t="n">
         <v>774</v>
@@ -14671,10 +14671,10 @@
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K230" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="L230" t="n">
         <v>3</v>
@@ -17012,7 +17012,7 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F268" t="n">
         <v>45</v>
@@ -17027,10 +17027,10 @@
         <v>0</v>
       </c>
       <c r="J268" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K268" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -17570,7 +17570,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F277" t="n">
         <v>229</v>
@@ -17585,10 +17585,10 @@
         <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K277" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L277" t="n">
         <v>4</v>
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F295" t="n">
         <v>174</v>
@@ -18701,10 +18701,10 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K295" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F319" t="n">
         <v>7</v>
@@ -20189,10 +20189,10 @@
         <v>0</v>
       </c>
       <c r="J319" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K319" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L319" t="n">
         <v>1</v>

--- a/data/raw/inventory/Week 30/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 30/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F37" t="n">
         <v>4</v>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2708,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F42" t="n">
         <v>16</v>
@@ -3009,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3434,16 +3434,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3685,13 +3685,13 @@
         <v>13</v>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -3747,13 +3747,13 @@
         <v>23</v>
       </c>
       <c r="F54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -4001,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -4063,16 +4063,16 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -4305,13 +4305,13 @@
         <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -4677,13 +4677,13 @@
         <v>3</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -4754,7 +4754,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
         <v>15</v>
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L73" t="n">
         <v>1</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F77" t="n">
         <v>7</v>
@@ -5179,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -5294,25 +5294,25 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F79" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -7157,13 +7157,13 @@
         <v>2</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
@@ -7591,13 +7591,13 @@
         <v>4</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F121" t="n">
         <v>3</v>
@@ -7907,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -7916,7 +7916,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F125" t="n">
         <v>2</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -8164,7 +8164,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -8332,16 +8332,16 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="F128" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
         <v>3</v>
       </c>
       <c r="K128" t="n">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
@@ -8394,16 +8394,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -9023,7 +9023,7 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -9032,7 +9032,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
@@ -9333,16 +9333,16 @@
         <v>0</v>
       </c>
       <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
         <v>2</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="n">
-        <v>3</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F147" t="n">
         <v>2</v>
@@ -9519,7 +9519,7 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -9528,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F148" t="n">
         <v>1</v>
@@ -9581,16 +9581,16 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
         <v>2</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="n">
-        <v>3</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F156" t="n">
         <v>2</v>
@@ -10083,10 +10083,10 @@
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F158" t="n">
         <v>2</v>
@@ -10201,16 +10201,16 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F163" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -10520,7 +10520,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F164" t="n">
         <v>14</v>
@@ -10579,10 +10579,10 @@
         <v>2</v>
       </c>
       <c r="J164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -10939,13 +10939,13 @@
         <v>11</v>
       </c>
       <c r="F170" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
@@ -11249,7 +11249,7 @@
         <v>2</v>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -11261,7 +11261,7 @@
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K175" t="n">
         <v>2</v>
@@ -12923,13 +12923,13 @@
         <v>9</v>
       </c>
       <c r="F202" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -13109,13 +13109,13 @@
         <v>3</v>
       </c>
       <c r="F205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F223" t="n">
         <v>10</v>
@@ -14231,7 +14231,7 @@
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I223" t="n">
         <v>0</v>
@@ -14240,7 +14240,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L223" t="n">
         <v>1</v>
@@ -14284,25 +14284,25 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F224" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I224" t="n">
         <v>0</v>
       </c>
       <c r="J224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -14408,16 +14408,16 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F226" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -14426,7 +14426,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -14656,25 +14656,25 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="F230" t="n">
-        <v>774</v>
+        <v>792</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K230" t="n">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="L230" t="n">
         <v>3</v>
@@ -16705,13 +16705,13 @@
         <v>2</v>
       </c>
       <c r="F263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
       </c>
       <c r="H263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I263" t="n">
         <v>0</v>
@@ -16950,10 +16950,10 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F267" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -16968,7 +16968,7 @@
         <v>5</v>
       </c>
       <c r="K267" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -17012,25 +17012,25 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F268" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I268" t="n">
         <v>0</v>
       </c>
       <c r="J268" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K268" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -17136,7 +17136,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F270" t="n">
         <v>18</v>
@@ -17145,16 +17145,16 @@
         <v>0</v>
       </c>
       <c r="H270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I270" t="n">
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -17384,16 +17384,16 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F274" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I274" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
         <v>1</v>
       </c>
       <c r="K274" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L274" t="n">
         <v>1</v>
@@ -17570,10 +17570,10 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F277" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -17585,10 +17585,10 @@
         <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L277" t="n">
         <v>4</v>
@@ -17821,13 +17821,13 @@
         <v>4</v>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I281" t="n">
         <v>0</v>
@@ -18252,7 +18252,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F288" t="n">
         <v>6</v>
@@ -18261,7 +18261,7 @@
         <v>0</v>
       </c>
       <c r="H288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I288" t="n">
         <v>0</v>
@@ -18270,7 +18270,7 @@
         <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -18456,10 +18456,10 @@
         <v>4</v>
       </c>
       <c r="K291" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M291" t="n">
         <v>0</v>
@@ -18686,25 +18686,25 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F295" t="n">
+        <v>173</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
         <v>174</v>
-      </c>
-      <c r="G295" t="n">
-        <v>0</v>
-      </c>
-      <c r="H295" t="n">
-        <v>0</v>
-      </c>
-      <c r="I295" t="n">
-        <v>0</v>
-      </c>
-      <c r="J295" t="n">
-        <v>0</v>
-      </c>
-      <c r="K295" t="n">
-        <v>175</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -18934,25 +18934,25 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="F299" t="n">
-        <v>779</v>
+        <v>792</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
       </c>
       <c r="H299" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I299" t="n">
         <v>0</v>
       </c>
       <c r="J299" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K299" t="n">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="L299" t="n">
         <v>7</v>
@@ -19120,7 +19120,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F302" t="n">
         <v>4</v>
@@ -19129,7 +19129,7 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I302" t="n">
         <v>0</v>
@@ -19138,7 +19138,7 @@
         <v>1</v>
       </c>
       <c r="K302" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L302" t="n">
         <v>0</v>
@@ -19182,25 +19182,25 @@
         </is>
       </c>
       <c r="E303" t="n">
+        <v>482</v>
+      </c>
+      <c r="F303" t="n">
+        <v>443</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="n">
+        <v>34</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>2</v>
+      </c>
+      <c r="K303" t="n">
         <v>484</v>
-      </c>
-      <c r="F303" t="n">
-        <v>429</v>
-      </c>
-      <c r="G303" t="n">
-        <v>0</v>
-      </c>
-      <c r="H303" t="n">
-        <v>51</v>
-      </c>
-      <c r="I303" t="n">
-        <v>0</v>
-      </c>
-      <c r="J303" t="n">
-        <v>1</v>
-      </c>
-      <c r="K303" t="n">
-        <v>486</v>
       </c>
       <c r="L303" t="n">
         <v>2</v>
@@ -19306,25 +19306,25 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G305" t="n">
         <v>0</v>
       </c>
       <c r="H305" t="n">
+        <v>2</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
         <v>4</v>
-      </c>
-      <c r="I305" t="n">
-        <v>0</v>
-      </c>
-      <c r="J305" t="n">
-        <v>0</v>
-      </c>
-      <c r="K305" t="n">
-        <v>5</v>
       </c>
       <c r="L305" t="n">
         <v>0</v>
@@ -19495,13 +19495,13 @@
         <v>9</v>
       </c>
       <c r="F308" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G308" t="n">
         <v>0</v>
       </c>
       <c r="H308" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I308" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F311" t="n">
         <v>21</v>
@@ -19687,7 +19687,7 @@
         <v>0</v>
       </c>
       <c r="H311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I311" t="n">
         <v>0</v>
@@ -19696,7 +19696,7 @@
         <v>0</v>
       </c>
       <c r="K311" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -19988,7 +19988,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F316" t="n">
         <v>15</v>
@@ -20003,10 +20003,10 @@
         <v>0</v>
       </c>
       <c r="J316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K316" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
@@ -20053,13 +20053,13 @@
         <v>3</v>
       </c>
       <c r="F317" t="n">
+        <v>2</v>
+      </c>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
+      <c r="H317" t="n">
         <v>1</v>
-      </c>
-      <c r="G317" t="n">
-        <v>0</v>
-      </c>
-      <c r="H317" t="n">
-        <v>2</v>
       </c>
       <c r="I317" t="n">
         <v>0</v>
@@ -20174,10 +20174,10 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F319" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G319" t="n">
         <v>0</v>
@@ -20192,7 +20192,7 @@
         <v>1</v>
       </c>
       <c r="K319" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L319" t="n">
         <v>1</v>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F322" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G322" t="n">
         <v>0</v>
@@ -20378,7 +20378,7 @@
         <v>1</v>
       </c>
       <c r="K322" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L322" t="n">
         <v>0</v>
@@ -20484,10 +20484,10 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F324" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G324" t="n">
         <v>0</v>
@@ -20502,7 +20502,7 @@
         <v>1</v>
       </c>
       <c r="K324" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -20732,10 +20732,10 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F328" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G328" t="n">
         <v>0</v>
@@ -20750,7 +20750,7 @@
         <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L328" t="n">
         <v>0</v>
@@ -20794,7 +20794,7 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F329" t="n">
         <v>0</v>
@@ -20803,7 +20803,7 @@
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I329" t="n">
         <v>0</v>
@@ -20812,7 +20812,7 @@
         <v>1</v>
       </c>
       <c r="K329" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
@@ -21665,13 +21665,13 @@
         <v>9</v>
       </c>
       <c r="F343" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G343" t="n">
         <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I343" t="n">
         <v>0</v>
@@ -21786,25 +21786,25 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F345" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G345" t="n">
         <v>0</v>
       </c>
       <c r="H345" t="n">
+        <v>1</v>
+      </c>
+      <c r="I345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J345" t="n">
         <v>2</v>
       </c>
-      <c r="I345" t="n">
-        <v>0</v>
-      </c>
-      <c r="J345" t="n">
-        <v>0</v>
-      </c>
       <c r="K345" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -22161,7 +22161,7 @@
         <v>5</v>
       </c>
       <c r="F351" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G351" t="n">
         <v>0</v>
@@ -22173,7 +22173,7 @@
         <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K351" t="n">
         <v>5</v>
@@ -22471,13 +22471,13 @@
         <v>20</v>
       </c>
       <c r="F356" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G356" t="n">
         <v>0</v>
       </c>
       <c r="H356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I356" t="n">
         <v>0</v>
@@ -23773,7 +23773,7 @@
         <v>2</v>
       </c>
       <c r="F377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G377" t="n">
         <v>0</v>
@@ -23785,7 +23785,7 @@
         <v>0</v>
       </c>
       <c r="J377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K377" t="n">
         <v>2</v>
@@ -23959,7 +23959,7 @@
         <v>30</v>
       </c>
       <c r="F380" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G380" t="n">
         <v>0</v>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="J380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K380" t="n">
         <v>30</v>
@@ -24083,13 +24083,13 @@
         <v>16</v>
       </c>
       <c r="F382" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
       </c>
       <c r="H382" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I382" t="n">
         <v>0</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F395" t="n">
         <v>5</v>
@@ -24895,7 +24895,7 @@
         <v>0</v>
       </c>
       <c r="H395" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I395" t="n">
         <v>0</v>
@@ -24904,7 +24904,7 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L395" t="n">
         <v>0</v>
@@ -24948,25 +24948,25 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F396" t="n">
+        <v>1</v>
+      </c>
+      <c r="G396" t="n">
+        <v>0</v>
+      </c>
+      <c r="H396" t="n">
         <v>3</v>
       </c>
-      <c r="G396" t="n">
-        <v>0</v>
-      </c>
-      <c r="H396" t="n">
-        <v>5</v>
-      </c>
       <c r="I396" t="n">
         <v>0</v>
       </c>
       <c r="J396" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K396" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L396" t="n">
         <v>0</v>
@@ -25010,7 +25010,7 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F397" t="n">
         <v>0</v>
@@ -25019,7 +25019,7 @@
         <v>0</v>
       </c>
       <c r="H397" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I397" t="n">
         <v>0</v>
@@ -25028,7 +25028,7 @@
         <v>0</v>
       </c>
       <c r="K397" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L397" t="n">
         <v>0</v>
@@ -25692,16 +25692,16 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F408" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G408" t="n">
         <v>0</v>
       </c>
       <c r="H408" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I408" t="n">
         <v>0</v>
@@ -25710,7 +25710,7 @@
         <v>1</v>
       </c>
       <c r="K408" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L408" t="n">
         <v>0</v>
@@ -25754,7 +25754,7 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F409" t="n">
         <v>8</v>
@@ -25763,16 +25763,16 @@
         <v>0</v>
       </c>
       <c r="H409" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I409" t="n">
         <v>0</v>
       </c>
       <c r="J409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K409" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L409" t="n">
         <v>0</v>
@@ -25878,7 +25878,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F411" t="n">
         <v>7</v>
@@ -25893,10 +25893,10 @@
         <v>0</v>
       </c>
       <c r="J411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K411" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L411" t="n">
         <v>0</v>
@@ -26315,7 +26315,7 @@
         <v>5</v>
       </c>
       <c r="F418" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
         <v>0</v>
       </c>
       <c r="J418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K418" t="n">
         <v>5</v>
